--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-device.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:13:23+00:00</t>
+    <t>2026-06-19T14:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1526,7 +1526,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>

--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-device.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:20:56+00:00</t>
+    <t>2026-06-16T14:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -1526,7 +1526,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
 </t>
   </si>
   <si>
